--- a/output/2026-09-08_00_Croazia_Zagrebacka_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-08_00_Croazia_Zagrebacka_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Verificato. Distributore dal 1987 di macchine e utensili per lavorazione metalli (CNC, macchine convenzionali, utensili di misura e taglio). Sede: Stara cesta 14, Mala Rakovica, 10430 Samobor.</t>
+          <t>Verificato. Distributore dal 1987 di macchine e utensili per lavorazione metalli (CNC, macchine convenzionali, utensili di misura e taglio). Sede: Stara cesta 14, Mala Rakovica, 10430 Samobor. [DUPLICATO — vedi anche: 2026-09-07_23_Croazia_Zagrebacka_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -578,7 +578,6 @@
           <t>+385 1 3438 190</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Verificato. Distributore utensili per lavorazione metalli. Sede legale a Cakovec, demo center 600mq a Novaki Samoborski (Zagrebacka zupanija). Email non reperita da fonti pubbliche.</t>
@@ -623,7 +622,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Verificato. Distributore utensili professionali (Ruko, Wiha, Dewalt, Bosch, Makita), attivo dal 1992. Sede: Ulica Ilije Gregorica 31, Prigorje Brdovecko, Brdovec.</t>
+          <t>Verificato. Distributore utensili professionali (Ruko, Wiha, Dewalt, Bosch, Makita), attivo dal 1992. Sede: Ulica Ilije Gregorica 31, Prigorje Brdovecko, Brdovec. [DUPLICATO — vedi anche: 2026-09-07_23_Croazia_Zagrebacka_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -658,7 +657,6 @@
           <t>01 2795 674</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Verificato come esistente, punto vendita rete Grupa Kolor. Vende metalna galanterija, vijcana roba, utensili da taglio/molatura. Profilo piu generico (ferramenta tecnica) rispetto agli altri distributori specializzati.</t>

--- a/output/2026-09-08_00_Croazia_Zagrebacka_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-08_00_Croazia_Zagrebacka_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
